--- a/Result/profitability/3615.xlsx
+++ b/Result/profitability/3615.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>20.93875</v>
+        <v>21.01375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>21.8825</v>
+        <v>21.6225</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>20.44</v>
+        <v>19.54</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -997,7 +997,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>17.53375</v>
+        <v>15.8275</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>11.90125</v>
+        <v>11.125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>12.12625</v>
+        <v>11.05</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>12.28625</v>
+        <v>11.00375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>8.071249999999999</v>
+        <v>8.071250000000001</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -9764,6 +9764,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3615</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>170</v>
+      </c>
+      <c r="D75" t="n">
+        <v>147</v>
+      </c>
+      <c r="E75" t="n">
+        <v>23</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-42</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-24.93%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>178</v>
+      </c>
+      <c r="J75" t="n">
+        <v>136</v>
+      </c>
+      <c r="K75" t="n">
+        <v>138</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.41625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X75" t="n">
+        <v>11.5625</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-10.26</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4319999999999999</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-26.125</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-13.65</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.5029476787030214</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
